--- a/inputs/order_dataset.xlsx
+++ b/inputs/order_dataset.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\DISS\03_Arbeitspakete\04_Framework\02_Modell\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\DISS\03_Arbeitspakete\04_Framework\03_Paper\Inhalte\Use Case Repo\disposition_framework_usecase\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65564A2E-5A4F-4A2A-B73A-4FDB97D411C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F46D31-118E-45D1-98DE-196E686FA012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orders" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">orders!$C$1:$F$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">orders!$C$1:$F$167</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="68">
   <si>
     <t>97076 Würzburg Deutschland</t>
   </si>
@@ -110,16 +110,7 @@
     <t>91126 Schwabach Deutschland</t>
   </si>
   <si>
-    <t>74405 Gaildorf Deutschland</t>
-  </si>
-  <si>
-    <t>57489 Drolshagen Deutschland</t>
-  </si>
-  <si>
     <t>58300 Wetter (Ruhr) Deutschland</t>
-  </si>
-  <si>
-    <t>58091 Hagen Deutschland</t>
   </si>
   <si>
     <t>74532 Ilshofen Deutschland</t>
@@ -628,37 +619,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G179"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G167"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.26953125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.36328125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="22.453125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="24.81640625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="23.7265625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="10.1796875" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="33.21875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="24.77734375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="G1" s="2"/>
     </row>
@@ -707,7 +698,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="12">
         <v>46195</v>
@@ -907,7 +898,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C14" s="12">
         <v>46195</v>
@@ -927,7 +918,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C15" s="12">
         <v>46195.333333333336</v>
@@ -947,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C16" s="12">
         <v>46196</v>
@@ -1047,7 +1038,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C21" s="12">
         <v>46196.291666666664</v>
@@ -1127,7 +1118,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C25" s="12">
         <v>46196</v>
@@ -1167,7 +1158,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C27" s="12">
         <v>46196</v>
@@ -1287,7 +1278,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C33" s="12">
         <v>46196</v>
@@ -1544,10 +1535,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="12">
         <v>46197</v>
@@ -1564,10 +1555,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C47" s="12">
         <v>46197</v>
@@ -1584,10 +1575,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C48" s="12">
         <v>46197</v>
@@ -1604,10 +1595,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C49" s="12">
         <v>46197</v>
@@ -1624,10 +1615,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C50" s="12">
         <v>46197</v>
@@ -1644,10 +1635,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C51" s="12">
         <v>46197</v>
@@ -1664,10 +1655,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>7</v>
       </c>
       <c r="C52" s="12">
         <v>46197</v>
@@ -1684,70 +1675,70 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C53" s="12">
-        <v>46197.291666666664</v>
+        <v>46197</v>
       </c>
       <c r="D53" s="12">
-        <v>46197.641655092593</v>
+        <v>46197.999305555553</v>
       </c>
       <c r="E53" s="12">
-        <v>46197.291666666664</v>
+        <v>46197</v>
       </c>
       <c r="F53" s="12">
-        <v>46197.599988425929</v>
+        <v>46197.683321759258</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C54" s="12">
-        <v>46197.291666666664</v>
+        <v>46197</v>
       </c>
       <c r="D54" s="12">
-        <v>46197.641655092593</v>
+        <v>46197.999305555553</v>
       </c>
       <c r="E54" s="12">
-        <v>46197.291666666664</v>
+        <v>46197</v>
       </c>
       <c r="F54" s="12">
-        <v>46197.599988425929</v>
+        <v>46197.999305555553</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C55" s="12">
-        <v>46197.291666666664</v>
+        <v>46197</v>
       </c>
       <c r="D55" s="12">
-        <v>46197.599988425929</v>
+        <v>46197.999305555553</v>
       </c>
       <c r="E55" s="12">
-        <v>46197.291666666664</v>
+        <v>46197</v>
       </c>
       <c r="F55" s="12">
-        <v>46197.599988425929</v>
+        <v>46197.999305555553</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C56" s="12">
         <v>46197</v>
@@ -1764,10 +1755,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" s="12">
         <v>46197</v>
@@ -1784,10 +1775,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C58" s="12">
         <v>46197</v>
@@ -1807,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C59" s="12">
         <v>46197</v>
@@ -1824,10 +1815,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C60" s="12">
         <v>46197</v>
@@ -1844,10 +1835,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C61" s="12">
         <v>46197</v>
@@ -1864,10 +1855,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C62" s="12">
         <v>46197</v>
@@ -1876,18 +1867,18 @@
         <v>46197.999305555553</v>
       </c>
       <c r="E62" s="12">
-        <v>46197</v>
+        <v>46197.458333333336</v>
       </c>
       <c r="F62" s="12">
-        <v>46197.999305555553</v>
+        <v>46197.516655092593</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63" s="12">
         <v>46197</v>
@@ -1904,30 +1895,30 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C64" s="12">
-        <v>46197</v>
+        <v>46197.375</v>
       </c>
       <c r="D64" s="12">
-        <v>46197.999305555553</v>
+        <v>46197.599988425929</v>
       </c>
       <c r="E64" s="12">
-        <v>46197</v>
+        <v>46197.333333333336</v>
       </c>
       <c r="F64" s="12">
-        <v>46197.999305555553</v>
+        <v>46197.516655092593</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C65" s="12">
         <v>46197</v>
@@ -1939,15 +1930,15 @@
         <v>46197</v>
       </c>
       <c r="F65" s="12">
-        <v>46197.683321759258</v>
+        <v>46197.999305555553</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C66" s="12">
         <v>46197</v>
@@ -1967,7 +1958,7 @@
         <v>12</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C67" s="12">
         <v>46197</v>
@@ -1984,10 +1975,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C68" s="12">
         <v>46197</v>
@@ -2007,27 +1998,27 @@
         <v>6</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C69" s="12">
-        <v>46197</v>
+        <v>46197.333333333336</v>
       </c>
       <c r="D69" s="12">
-        <v>46197.999305555553</v>
+        <v>46197.683321759258</v>
       </c>
       <c r="E69" s="12">
-        <v>46197</v>
+        <v>46197.333333333336</v>
       </c>
       <c r="F69" s="12">
-        <v>46197.999305555553</v>
+        <v>46197.683321759258</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C70" s="12">
         <v>46197</v>
@@ -2044,10 +2035,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C71" s="12">
         <v>46197</v>
@@ -2064,182 +2055,182 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C72" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D72" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E72" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F72" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D73" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E73" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F73" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="C74" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D74" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E74" s="12">
-        <v>46197.458333333336</v>
+        <v>46198</v>
       </c>
       <c r="F74" s="12">
-        <v>46197.516655092593</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C75" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D75" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E75" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F75" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="C76" s="12">
-        <v>46197.375</v>
+        <v>46198</v>
       </c>
       <c r="D76" s="12">
-        <v>46197.599988425929</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E76" s="12">
-        <v>46197.333333333336</v>
+        <v>46198</v>
       </c>
       <c r="F76" s="12">
-        <v>46197.516655092593</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C77" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D77" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E77" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F77" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C78" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D78" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E78" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F78" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C79" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D79" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E79" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F79" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C80" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D80" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E80" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F80" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2247,67 +2238,67 @@
         <v>6</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C81" s="12">
-        <v>46197.333333333336</v>
+        <v>46198</v>
       </c>
       <c r="D81" s="12">
-        <v>46197.683321759258</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E81" s="12">
-        <v>46197.333333333336</v>
+        <v>46198</v>
       </c>
       <c r="F81" s="12">
-        <v>46197.683321759258</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C82" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D82" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E82" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F82" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C83" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D83" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E83" s="12">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="F83" s="12">
-        <v>46197.999305555553</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C84" s="12">
         <v>46198</v>
@@ -2324,10 +2315,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C85" s="12">
         <v>46198</v>
@@ -2344,10 +2335,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C86" s="12">
         <v>46198</v>
@@ -2364,10 +2355,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C87" s="12">
         <v>46198</v>
@@ -2384,10 +2375,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C88" s="12">
         <v>46198</v>
@@ -2404,10 +2395,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C89" s="12">
         <v>46198</v>
@@ -2424,10 +2415,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90" s="12">
         <v>46198</v>
@@ -2444,7 +2435,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>6</v>
@@ -2464,10 +2455,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C92" s="12">
         <v>46198</v>
@@ -2484,7 +2475,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>6</v>
@@ -2504,10 +2495,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C94" s="12">
         <v>46198</v>
@@ -2524,10 +2515,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C95" s="12">
         <v>46198</v>
@@ -2544,10 +2535,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C96" s="12">
         <v>46198</v>
@@ -2564,10 +2555,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C97" s="12">
         <v>46198</v>
@@ -2584,10 +2575,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C98" s="12">
         <v>46198</v>
@@ -2604,30 +2595,30 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C99" s="12">
-        <v>46198</v>
+        <v>46198.333333333336</v>
       </c>
       <c r="D99" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.479166666664</v>
       </c>
       <c r="E99" s="12">
-        <v>46198</v>
+        <v>46198.333333333336</v>
       </c>
       <c r="F99" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.479166666664</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C100" s="12">
         <v>46198</v>
@@ -2644,10 +2635,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C101" s="12">
         <v>46198</v>
@@ -2656,15 +2647,15 @@
         <v>46198.999305555553</v>
       </c>
       <c r="E101" s="12">
-        <v>46198</v>
+        <v>46198.583333333336</v>
       </c>
       <c r="F101" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.683321759258</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>6</v>
@@ -2704,10 +2695,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C104" s="12">
         <v>46198</v>
@@ -2724,10 +2715,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C105" s="12">
         <v>46198</v>
@@ -2744,10 +2735,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C106" s="12">
         <v>46198</v>
@@ -2764,10 +2755,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C107" s="12">
         <v>46198</v>
@@ -2784,42 +2775,42 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C108" s="12">
-        <v>46198</v>
+        <v>46198.291666666664</v>
       </c>
       <c r="D108" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.599988425929</v>
       </c>
       <c r="E108" s="12">
-        <v>46198</v>
+        <v>46198.291666666664</v>
       </c>
       <c r="F108" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.599988425929</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C109" s="12">
-        <v>46198</v>
+        <v>46198.291666666664</v>
       </c>
       <c r="D109" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.599988425929</v>
       </c>
       <c r="E109" s="12">
-        <v>46198</v>
+        <v>46198.291666666664</v>
       </c>
       <c r="F109" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.599988425929</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -2830,44 +2821,44 @@
         <v>57</v>
       </c>
       <c r="C110" s="12">
-        <v>46198</v>
+        <v>46198.541666666664</v>
       </c>
       <c r="D110" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.683321759258</v>
       </c>
       <c r="E110" s="12">
-        <v>46198</v>
+        <v>46198.291666666664</v>
       </c>
       <c r="F110" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.599988425929</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="C111" s="12">
-        <v>46198.333333333336</v>
+        <v>46198.541666666664</v>
       </c>
       <c r="D111" s="12">
-        <v>46198.479166666664</v>
+        <v>46198.683321759258</v>
       </c>
       <c r="E111" s="12">
-        <v>46198.333333333336</v>
+        <v>46198.291666666664</v>
       </c>
       <c r="F111" s="12">
-        <v>46198.479166666664</v>
+        <v>46198.599988425929</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C112" s="12">
         <v>46198</v>
@@ -2884,10 +2875,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C113" s="12">
         <v>46198</v>
@@ -2896,18 +2887,18 @@
         <v>46198.999305555553</v>
       </c>
       <c r="E113" s="12">
-        <v>46198.583333333336</v>
+        <v>46198</v>
       </c>
       <c r="F113" s="12">
-        <v>46198.683321759258</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C114" s="12">
         <v>46198</v>
@@ -2924,10 +2915,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C115" s="12">
         <v>46198</v>
@@ -2944,10 +2935,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C116" s="12">
         <v>46198</v>
@@ -2964,10 +2955,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B117" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>7</v>
       </c>
       <c r="C117" s="12">
         <v>46198</v>
@@ -2984,10 +2975,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C118" s="12">
         <v>46198</v>
@@ -3004,10 +2995,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C119" s="12">
         <v>46198</v>
@@ -3024,42 +3015,42 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C120" s="12">
-        <v>46198.291666666664</v>
+        <v>46198</v>
       </c>
       <c r="D120" s="12">
-        <v>46198.599988425929</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E120" s="12">
-        <v>46198.291666666664</v>
+        <v>46198</v>
       </c>
       <c r="F120" s="12">
-        <v>46198.599988425929</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C121" s="12">
-        <v>46198.291666666664</v>
+        <v>46198</v>
       </c>
       <c r="D121" s="12">
-        <v>46198.599988425929</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E121" s="12">
-        <v>46198.291666666664</v>
+        <v>46198</v>
       </c>
       <c r="F121" s="12">
-        <v>46198.599988425929</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3067,47 +3058,47 @@
         <v>6</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C122" s="12">
-        <v>46198.541666666664</v>
+        <v>46198</v>
       </c>
       <c r="D122" s="12">
-        <v>46198.683321759258</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E122" s="12">
-        <v>46198.291666666664</v>
+        <v>46198</v>
       </c>
       <c r="F122" s="12">
-        <v>46198.599988425929</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C123" s="12">
-        <v>46198.541666666664</v>
+        <v>46198</v>
       </c>
       <c r="D123" s="12">
-        <v>46198.683321759258</v>
+        <v>46198.999305555553</v>
       </c>
       <c r="E123" s="12">
-        <v>46198.291666666664</v>
+        <v>46198</v>
       </c>
       <c r="F123" s="12">
-        <v>46198.599988425929</v>
+        <v>46198.999305555553</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C124" s="12">
         <v>46198</v>
@@ -3119,15 +3110,15 @@
         <v>46198</v>
       </c>
       <c r="F124" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.766655092593</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C125" s="12">
         <v>46198</v>
@@ -3144,10 +3135,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C126" s="12">
         <v>46198</v>
@@ -3164,10 +3155,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C127" s="12">
         <v>46198</v>
@@ -3184,10 +3175,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C128" s="12">
         <v>46198</v>
@@ -3204,10 +3195,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C129" s="12">
         <v>46198</v>
@@ -3224,10 +3215,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="C130" s="12">
         <v>46198</v>
@@ -3239,15 +3230,15 @@
         <v>46198</v>
       </c>
       <c r="F130" s="12">
-        <v>46198.999305555553</v>
+        <v>46198.558321759258</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C131" s="12">
         <v>46198</v>
@@ -3264,250 +3255,250 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C132" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D132" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E132" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F132" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C133" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="D133" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
       <c r="E133" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="F133" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C134" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="D134" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
       <c r="E134" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="F134" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C135" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="D135" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
       <c r="E135" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="F135" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="C136" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="D136" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
       <c r="E136" s="12">
-        <v>46198</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="F136" s="12">
-        <v>46198.766655092593</v>
+        <v>46199.641655092593</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C137" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D137" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E137" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F137" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C138" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D138" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E138" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F138" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C139" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D139" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E139" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F139" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="C140" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D140" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E140" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F140" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="C141" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D141" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E141" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F141" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C142" s="12">
-        <v>46198</v>
+        <v>46199.3125</v>
       </c>
       <c r="D142" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.349988425929</v>
       </c>
       <c r="E142" s="12">
-        <v>46198</v>
+        <v>46199.5</v>
       </c>
       <c r="F142" s="12">
-        <v>46198.558321759258</v>
+        <v>46199.641655092593</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C143" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D143" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E143" s="12">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F143" s="12">
-        <v>46198.999305555553</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C144" s="12">
         <v>46199</v>
@@ -3524,87 +3515,87 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C145" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="D145" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E145" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="F145" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C146" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="D146" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E146" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="F146" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C147" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="D147" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E147" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="F147" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C148" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="D148" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E148" s="12">
-        <v>46199.302083333336</v>
+        <v>46199</v>
       </c>
       <c r="F148" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>6</v>
@@ -3624,7 +3615,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>6</v>
@@ -3644,7 +3635,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>6</v>
@@ -3664,10 +3655,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C152" s="12">
         <v>46199</v>
@@ -3684,10 +3675,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C153" s="12">
         <v>46199</v>
@@ -3704,90 +3695,90 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C154" s="12">
-        <v>46199.3125</v>
+        <v>46199</v>
       </c>
       <c r="D154" s="12">
-        <v>46199.349988425929</v>
+        <v>46199.999305555553</v>
       </c>
       <c r="E154" s="12">
-        <v>46199.5</v>
+        <v>46199</v>
       </c>
       <c r="F154" s="12">
-        <v>46199.641655092593</v>
+        <v>46199.999305555553</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C155" s="12">
-        <v>46199</v>
+        <v>46199.583333333336</v>
       </c>
       <c r="D155" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.683321759258</v>
       </c>
       <c r="E155" s="12">
-        <v>46199</v>
+        <v>46199.291666666664</v>
       </c>
       <c r="F155" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.599988425929</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C156" s="12">
-        <v>46199</v>
+        <v>46199.583333333336</v>
       </c>
       <c r="D156" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.683321759258</v>
       </c>
       <c r="E156" s="12">
-        <v>46199</v>
+        <v>46199.291666666664</v>
       </c>
       <c r="F156" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.599988425929</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C157" s="12">
-        <v>46199</v>
+        <v>46199.583333333336</v>
       </c>
       <c r="D157" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.683321759258</v>
       </c>
       <c r="E157" s="12">
-        <v>46199</v>
+        <v>46199.291666666664</v>
       </c>
       <c r="F157" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.599988425929</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C158" s="12">
         <v>46199</v>
@@ -3804,10 +3795,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C159" s="12">
         <v>46199</v>
@@ -3824,10 +3815,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C160" s="12">
         <v>46199</v>
@@ -3844,16 +3835,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C161" s="12">
-        <v>46199</v>
+        <v>46199.416666666664</v>
       </c>
       <c r="D161" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
       <c r="E161" s="12">
         <v>46199</v>
@@ -3864,10 +3855,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C162" s="12">
         <v>46199</v>
@@ -3884,10 +3875,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C163" s="12">
         <v>46199</v>
@@ -3924,301 +3915,61 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C165" s="12">
-        <v>46199</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="D165" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
       <c r="E165" s="12">
-        <v>46199</v>
+        <v>46199.302083333336</v>
       </c>
       <c r="F165" s="12">
-        <v>46199.999305555553</v>
+        <v>46199.641655092593</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B166" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C166" s="12">
+        <v>46199</v>
+      </c>
+      <c r="D166" s="12">
+        <v>46199.999305555553</v>
+      </c>
+      <c r="E166" s="12">
+        <v>46199</v>
+      </c>
+      <c r="F166" s="12">
+        <v>46199.999305555553</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C166" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D166" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E166" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F166" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C167" s="12">
-        <v>46199.583333333336</v>
-      </c>
-      <c r="D167" s="12">
-        <v>46199.683321759258</v>
-      </c>
-      <c r="E167" s="12">
-        <v>46199.291666666664</v>
-      </c>
-      <c r="F167" s="12">
-        <v>46199.599988425929</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C168" s="12">
-        <v>46199.583333333336</v>
-      </c>
-      <c r="D168" s="12">
-        <v>46199.683321759258</v>
-      </c>
-      <c r="E168" s="12">
-        <v>46199.291666666664</v>
-      </c>
-      <c r="F168" s="12">
-        <v>46199.599988425929</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C169" s="12">
-        <v>46199.583333333336</v>
-      </c>
-      <c r="D169" s="12">
-        <v>46199.683321759258</v>
-      </c>
-      <c r="E169" s="12">
-        <v>46199.291666666664</v>
-      </c>
-      <c r="F169" s="12">
-        <v>46199.599988425929</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C170" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D170" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E170" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F170" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C171" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D171" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E171" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F171" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C172" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D172" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E172" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F172" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C173" s="12">
-        <v>46199.416666666664</v>
-      </c>
-      <c r="D173" s="12">
-        <v>46199.641655092593</v>
-      </c>
-      <c r="E173" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F173" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C174" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D174" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E174" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F174" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D175" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E175" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F175" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C176" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D176" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E176" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F176" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B177" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C177" s="12">
-        <v>46199.302083333336</v>
-      </c>
-      <c r="D177" s="12">
-        <v>46199.641655092593</v>
-      </c>
-      <c r="E177" s="12">
-        <v>46199.302083333336</v>
-      </c>
-      <c r="F177" s="12">
-        <v>46199.641655092593</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C178" s="12">
-        <v>46199</v>
-      </c>
-      <c r="D178" s="12">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E178" s="12">
-        <v>46199</v>
-      </c>
-      <c r="F178" s="12">
-        <v>46199.999305555553</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B179" s="8" t="s">
+      <c r="B167" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C179" s="13">
-        <v>46199</v>
-      </c>
-      <c r="D179" s="13">
-        <v>46199.999305555553</v>
-      </c>
-      <c r="E179" s="13">
-        <v>46199</v>
-      </c>
-      <c r="F179" s="13">
+      <c r="C167" s="13">
+        <v>46199</v>
+      </c>
+      <c r="D167" s="13">
+        <v>46199.999305555553</v>
+      </c>
+      <c r="E167" s="13">
+        <v>46199</v>
+      </c>
+      <c r="F167" s="13">
         <v>46199.999305555553</v>
       </c>
     </row>
